--- a/Archivos/CONFIGURACION/Config.xlsx
+++ b/Archivos/CONFIGURACION/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Procesos_UiPath\00_GENERICOWindowsProcess_XX_XX_XX\Archivos\CONFIGURACION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\CONFIGURACION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11688C8E-F18B-4E72-BFE9-BE6ADD8E953C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40DE73E-8645-43D2-81CB-CC60AF1EFE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="228">
   <si>
     <t>Name</t>
   </si>
@@ -817,6 +817,12 @@
   </si>
   <si>
     <t>00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX</t>
+  </si>
+  <si>
+    <t>C:\Users\USR\AppData\Local\Programs\Python\Python38\</t>
+  </si>
+  <si>
+    <t>C:\Program Files\Python38\</t>
   </si>
 </sst>
 </file>
@@ -1640,10 +1646,16 @@
       <c r="A12" s="2" t="s">
         <v>142</v>
       </c>
+      <c r="B12" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="13" spans="1:26" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>143</v>
+      </c>
+      <c r="B13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">

--- a/Archivos/CONFIGURACION/Config.xlsx
+++ b/Archivos/CONFIGURACION/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\CONFIGURACION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40DE73E-8645-43D2-81CB-CC60AF1EFE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7025A53-1AAE-4513-8BF2-B1BEECB513C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Archivos/CONFIGURACION/Config.xlsx
+++ b/Archivos/CONFIGURACION/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\CONFIGURACION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Procesos_Uipath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\CONFIGURACION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7025A53-1AAE-4513-8BF2-B1BEECB513C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245EB908-4093-498D-A3D7-875DF2F7E1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="243">
   <si>
     <t>Name</t>
   </si>
@@ -568,9 +568,6 @@
   </si>
   <si>
     <t>Colocar el ID principal del espacio en drive</t>
-  </si>
-  <si>
-    <t>D:\Procesos_UiPath\Llaves\crp-pro-ccoe-automat-c9c501f57fdd_NF.json</t>
   </si>
   <si>
     <t>crp-pro-ccoe-automat-neg-finan@crp-pro-ccoe-automat.iam.gserviceaccount.com</t>
@@ -816,20 +813,68 @@
     <t>END POINTS PARA MODULO "CHAT_RPA"</t>
   </si>
   <si>
-    <t>00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX</t>
-  </si>
-  <si>
     <t>C:\Users\USR\AppData\Local\Programs\Python\Python38\</t>
   </si>
   <si>
     <t>C:\Program Files\Python38\</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>MedalliaUser</t>
+  </si>
+  <si>
+    <t>MedalliaPassword</t>
+  </si>
+  <si>
+    <t>cricardov@liverpool.com.mx</t>
+  </si>
+  <si>
+    <t>3ras3_un4JM</t>
+  </si>
+  <si>
+    <t>541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG</t>
+  </si>
+  <si>
+    <t>Descargas</t>
+  </si>
+  <si>
+    <t>Downloads\</t>
+  </si>
+  <si>
+    <t>0AHVIhGN0elUOUk9PVA</t>
+  </si>
+  <si>
+    <t>Id_Template_Liverpool</t>
+  </si>
+  <si>
+    <t>Template de Google Sheet de Liverpool</t>
+  </si>
+  <si>
+    <t>Id_Carpeta_Config_Bot</t>
+  </si>
+  <si>
+    <t>1MW2qJxEnyfY3t5gfL9MOCKiYjNtK1CNp</t>
+  </si>
+  <si>
+    <t>1ZUrDKGkjrHELaHsYlGOsv9Sxd8xapjPZQoTOnLnCYZQ</t>
+  </si>
+  <si>
+    <t>Id_Template_Suburbia</t>
+  </si>
+  <si>
+    <t>Template de Google Sheet de Suburbia</t>
+  </si>
+  <si>
+    <t>1UVfEf_Rn2nx13Ursoj0rYL7qGP5-346SpHQL_z-_0VM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -847,6 +892,7 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="6"/>
@@ -933,6 +979,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1050,12 +1103,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1171,9 +1225,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Accent2" xfId="2" builtinId="33"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
@@ -1493,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z988"/>
+  <dimension ref="A1:Z992"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.54296875" customWidth="1"/>
@@ -1544,10 +1601,13 @@
         <v>123</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C3" s="26" t="s">
         <v>128</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -1570,760 +1630,812 @@
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1">
+    <row r="6" spans="1:26" ht="14.5">
       <c r="A6" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="2" t="str">
-        <f>"D:\Procesos_UiPath\"&amp;B3&amp;"\Archivos\"</f>
-        <v>D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>133</v>
+        <v>232</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="str">
-        <f>"D:\Procesos_UiPath\"&amp;B3&amp;"\Archivos\"&amp;B4&amp;"\"</f>
-        <v>D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\Temporal\</v>
+        <f>_xlfn.CONCAT($E$3, ":\Procesos_UiPath\"&amp;B3&amp;"\Archivos\")</f>
+        <v>C:\Procesos_UiPath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <f>_xlfn.CONCAT($E$3, ":\Procesos_UiPath\"&amp;B3&amp;"\Archivos\"&amp;B4&amp;"\")</f>
+        <v>C:\Procesos_UiPath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\Temporal\</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="2" t="str">
-        <f>"D:\Procesos_UiPath\"&amp;B3&amp;"\Archivos\"&amp;B4&amp;""</f>
-        <v>D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\Temporal</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B9" s="2" t="str">
+        <f>_xlfn.CONCAT($E$3, ":\Procesos_UiPath\"&amp;B3&amp;"\Archivos\"&amp;B4&amp;"_Error")</f>
+        <v>C:\Procesos_UiPath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\Temporal_Error</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A9" t="s">
+    <row r="10" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A10" t="s">
         <v>48</v>
       </c>
-      <c r="B9" t="str">
-        <f>"D:\Procesos_UiPath\"&amp;B3&amp;"\Archivos\FORMATOS\"</f>
-        <v>D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\FORMATOS\</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B10" t="str">
+        <f>_xlfn.CONCAT($E$3, ":\Procesos_UiPath\"&amp;B3&amp;"\Archivos\FORMATOS\")</f>
+        <v>C:\Procesos_UiPath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\FORMATOS\</v>
+      </c>
+      <c r="C10" t="s">
         <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B10" s="2" t="str">
-        <f>"D:\Procesos_UiPath\"&amp;B3&amp;"\Archivos\CONFIGURACION\"</f>
-        <v>D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\CONFIGURACION\</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B11" s="2" t="str">
-        <f>"D:\Procesos_UiPath\"&amp;B3&amp;"\Archivos\Exceptions_Screenshots\"</f>
-        <v>D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\Exceptions_Screenshots\</v>
+        <f>_xlfn.CONCAT($E$3, ":\Procesos_UiPath\"&amp;B3&amp;"\Archivos\CONFIGURACION\")</f>
+        <v>C:\Procesos_UiPath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\CONFIGURACION\</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="2" t="str">
+        <f>_xlfn.CONCAT($E$3, ":\Procesos_UiPath\"&amp;B3&amp;"\Archivos\Exceptions_Screenshots\")</f>
+        <v>C:\Procesos_UiPath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\Exceptions_Screenshots\</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B12" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="14" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="B13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B13" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A14" s="10" t="s">
+      <c r="B14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A15" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-    </row>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1">
-      <c r="C15" s="2"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="17" spans="1:3" ht="14.25" customHeight="1">
+      <c r="C17" s="2"/>
+    </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A19" s="10" t="s">
+    <row r="19" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A20" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-    </row>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+    </row>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="23" spans="1:3" ht="14.5">
-      <c r="A23" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-    </row>
-    <row r="24" spans="1:3" ht="14" customHeight="1">
-      <c r="A24" s="2" t="s">
+    <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="24" spans="1:3" ht="14.5">
+      <c r="A24" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+    </row>
+    <row r="25" spans="1:3" ht="14" customHeight="1">
+      <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2" t="s">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A25" s="2" t="s">
+    <row r="26" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="4" t="s">
+      <c r="B26" s="2"/>
+      <c r="C26" s="4" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A28" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C28" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="29" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A29" s="10" t="s">
+    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A30" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-    </row>
-    <row r="30" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12"/>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A32" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="33" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A33" s="10" t="s">
+    <row r="33" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="34" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A34" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>146</v>
-      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
     </row>
     <row r="35" spans="1:4" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B35" t="s">
-        <v>148</v>
+        <v>51</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>148</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A38" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" t="s">
+      <c r="B38" s="28"/>
+      <c r="C38" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="14" customHeight="1">
-      <c r="A38" s="2" t="s">
+    <row r="39" spans="1:4" ht="14" customHeight="1">
+      <c r="A39" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>156</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A39" s="2" t="s">
+    <row r="40" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A40" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="13" customHeight="1">
-      <c r="A40" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="13" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="42" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A42" s="10" t="s">
+    <row r="42" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="43" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A43" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="180.5" customHeight="1">
-      <c r="A43" s="2" t="s">
+      <c r="B43" s="11"/>
+      <c r="C43" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="180.5" customHeight="1">
+      <c r="A44" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>148</v>
       </c>
-      <c r="C43" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D43" s="30"/>
-    </row>
-    <row r="44" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A44" s="2" t="s">
+      <c r="C44" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" s="30"/>
+    </row>
+    <row r="45" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A45" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="30"/>
-    </row>
-    <row r="45" spans="1:4" ht="14.25" customHeight="1">
-      <c r="D45" s="13"/>
+      <c r="D45" s="30"/>
     </row>
     <row r="46" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A46" s="12" t="s">
+      <c r="D46" s="13"/>
+    </row>
+    <row r="47" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A47" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-    </row>
-    <row r="47" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A47" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>175</v>
-      </c>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
     </row>
     <row r="48" spans="1:4" ht="14.25" customHeight="1">
       <c r="A48" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A49" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C48" s="8"/>
-    </row>
-    <row r="49" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A49" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" t="s">
-        <v>176</v>
-      </c>
-      <c r="D49" s="4"/>
+      <c r="C49" s="8"/>
     </row>
     <row r="50" spans="1:4" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>177</v>
+        <v>58</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" t="s">
+        <v>175</v>
       </c>
       <c r="D50" s="4"/>
     </row>
     <row r="51" spans="1:4" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D51" s="4"/>
+    </row>
+    <row r="52" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A52" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D51" s="4"/>
-    </row>
-    <row r="52" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A52" s="2" t="s">
+      <c r="C52" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="4"/>
+    </row>
+    <row r="53" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A53" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B53" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D52" s="34"/>
-    </row>
-    <row r="53" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A53" s="14" t="s">
+      <c r="D53" s="34"/>
+    </row>
+    <row r="54" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A54" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B54" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A54" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C54" s="32" t="s">
-        <v>179</v>
-      </c>
+      <c r="C54" s="31"/>
       <c r="D54" s="4"/>
     </row>
     <row r="55" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A55" s="15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C55" s="32" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D55" s="4"/>
     </row>
     <row r="56" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A56" s="15" t="s">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" s="32" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D56" s="4"/>
     </row>
     <row r="57" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A57" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D57" s="4"/>
     </row>
     <row r="58" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A58" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="D58" s="4"/>
+    </row>
+    <row r="59" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A59" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B59" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C58" s="32" t="s">
+      <c r="C59" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60" spans="1:4" ht="58.5" thickBot="1">
+      <c r="A60" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="D58" s="4"/>
-    </row>
-    <row r="59" spans="1:4" ht="58.5" thickBot="1">
-      <c r="A59" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" s="32" t="s">
+      <c r="D60" s="4"/>
+    </row>
+    <row r="61" spans="1:4" thickBot="1">
+      <c r="A61" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C61" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="D59" s="4"/>
-    </row>
-    <row r="60" spans="1:4" thickBot="1">
-      <c r="A60" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C60" s="32" t="s">
+      <c r="D61" s="4"/>
+    </row>
+    <row r="62" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A62" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="D60" s="4"/>
-    </row>
-    <row r="61" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A61" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B61" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C61" s="32" t="s">
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A63" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C63" s="33" t="s">
         <v>186</v>
-      </c>
-      <c r="D61" s="4"/>
-    </row>
-    <row r="62" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A62" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C62" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="D62" s="4"/>
-    </row>
-    <row r="63" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A63" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="B63" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="32" t="s">
-        <v>188</v>
       </c>
       <c r="D63" s="4"/>
     </row>
     <row r="64" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A64" s="15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D64" s="4"/>
     </row>
     <row r="65" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A65" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B65" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C65" s="32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D65" s="4"/>
     </row>
     <row r="66" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A66" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" t="s">
+        <v>85</v>
+      </c>
+      <c r="C66" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="D66" s="4"/>
+    </row>
+    <row r="67" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A67" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="32" t="s">
+      <c r="B67" s="15"/>
+      <c r="C67" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="D67" s="4"/>
+    </row>
+    <row r="68" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A68" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68" s="33" t="s">
         <v>189</v>
-      </c>
-      <c r="D66" s="4"/>
-    </row>
-    <row r="67" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A67" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B67" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="D67" s="4"/>
-    </row>
-    <row r="68" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A68" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B68" t="s">
-        <v>90</v>
-      </c>
-      <c r="C68" s="32" t="s">
-        <v>191</v>
       </c>
       <c r="D68" s="4"/>
     </row>
     <row r="69" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A69" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C69" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D69" s="4"/>
     </row>
     <row r="70" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A70" s="15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C70" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D70" s="4"/>
     </row>
     <row r="71" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A71" s="15" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C71" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D71" s="4"/>
     </row>
     <row r="72" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A72" s="15" t="s">
-        <v>166</v>
+        <v>97</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
-      </c>
-      <c r="C72" s="32"/>
+        <v>98</v>
+      </c>
+      <c r="C72" s="32" t="s">
+        <v>190</v>
+      </c>
       <c r="D72" s="4"/>
     </row>
     <row r="73" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A73" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="B73" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>193</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="B73" t="s">
+        <v>167</v>
+      </c>
+      <c r="C73" s="32"/>
+      <c r="D73" s="4"/>
     </row>
     <row r="74" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
       <c r="A74" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B74" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A75" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B75" t="s">
         <v>98</v>
       </c>
-      <c r="C74" s="32"/>
-    </row>
-    <row r="75" spans="1:4" ht="14.5" customHeight="1" thickBot="1">
-      <c r="A75" s="15" t="s">
+      <c r="C75" s="32"/>
+    </row>
+    <row r="76" spans="1:4" ht="14.5" customHeight="1" thickBot="1">
+      <c r="A76" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B76" t="s">
         <v>171</v>
       </c>
-      <c r="C75" s="32"/>
-    </row>
-    <row r="76" spans="1:4" ht="14.5" customHeight="1" thickBot="1">
-      <c r="A76" s="19" t="s">
+      <c r="C76" s="32"/>
+    </row>
+    <row r="77" spans="1:4" ht="14.5" customHeight="1" thickBot="1">
+      <c r="A77" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="B76" s="19" t="s">
+      <c r="B77" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C76" s="31" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A77" s="15"/>
-      <c r="B77" s="15"/>
-    </row>
-    <row r="78" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A78" s="20" t="s">
+      <c r="C77" s="31" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A78" s="15"/>
+      <c r="B78" s="15"/>
+    </row>
+    <row r="79" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A79" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-    </row>
-    <row r="79" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A79" t="s">
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+    </row>
+    <row r="80" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A80" t="s">
         <v>100</v>
       </c>
-      <c r="B79" s="2"/>
-      <c r="C79" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="44" customHeight="1">
-      <c r="C80" s="3"/>
-    </row>
-    <row r="81" spans="1:3" ht="51" customHeight="1">
-      <c r="B81" s="21"/>
-    </row>
-    <row r="82" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A82" s="36" t="s">
+      <c r="B80" s="2"/>
+      <c r="C80" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="44" customHeight="1">
+      <c r="C81" s="3"/>
+    </row>
+    <row r="82" spans="1:3" ht="51" customHeight="1">
+      <c r="B82" s="21"/>
+    </row>
+    <row r="83" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A83" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="B82" s="37"/>
-      <c r="C82" s="36"/>
-    </row>
-    <row r="83" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A83" s="38" t="s">
+      <c r="B83" s="37"/>
+      <c r="C83" s="36"/>
+    </row>
+    <row r="84" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A84" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B83" s="39"/>
-      <c r="C83" s="39" t="s">
+      <c r="B84" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="C84" s="39" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="51.5" customHeight="1">
-      <c r="A84" s="40" t="s">
+    <row r="85" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A85" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A86" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B86" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A87" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C87" s="2"/>
+    </row>
+    <row r="88" spans="1:3" ht="51.5" customHeight="1">
+      <c r="A88" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="B88" s="41" t="str">
+        <f>_xlfn.CONCAT(E3,":\Procesos_UiPath\Llaves\crp-pro-ccoe-automat-c9c501f57fdd_NF.json")</f>
+        <v>C:\Procesos_UiPath\Llaves\crp-pro-ccoe-automat-c9c501f57fdd_NF.json</v>
+      </c>
+      <c r="C88" s="42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="42" customHeight="1">
+      <c r="A89" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="B84" s="41" t="s">
+      <c r="B89" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="C84" s="42" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="42" customHeight="1">
-      <c r="A85" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="B85" s="43" t="s">
-        <v>174</v>
-      </c>
-      <c r="C85" s="42" t="s">
+      <c r="C89" s="42" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="14" customHeight="1">
-      <c r="A86" s="2" t="s">
+    <row r="90" spans="1:3" ht="14" customHeight="1">
+      <c r="A90" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B90" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A87" s="12" t="s">
+    <row r="91" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A91" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12"/>
-    </row>
-    <row r="88" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="89" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="90" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A90" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B90" s="12"/>
-      <c r="C90" s="12"/>
-    </row>
-    <row r="91" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A91" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="B91" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C91" s="22"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
     </row>
     <row r="92" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="93" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="94" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A94" s="12"/>
+      <c r="A94" s="12" t="s">
+        <v>106</v>
+      </c>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
     </row>
-    <row r="95" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="95" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A95" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B95" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C95" s="22"/>
+    </row>
     <row r="96" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="97" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="98" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A98" s="12"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12"/>
+    </row>
+    <row r="99" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="100" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="101" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="102" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="103" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A103" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" s="51" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A104" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="106" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="107" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="108" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="109" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="110" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="111" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="112" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="113" ht="14.25" customHeight="1"/>
     <row r="114" ht="14.25" customHeight="1"/>
     <row r="115" ht="14.25" customHeight="1"/>
@@ -3200,10 +3312,17 @@
     <row r="986" ht="14.25" customHeight="1"/>
     <row r="987" ht="14.25" customHeight="1"/>
     <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
+  <hyperlinks>
+    <hyperlink ref="B103" r:id="rId1" xr:uid="{635E4254-AF21-4D23-80EB-9B5D00625052}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3260,7 +3379,7 @@
         <v>20</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -3294,7 +3413,7 @@
         <v>126</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -3383,7 +3502,7 @@
         <v>122</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.5">
@@ -3394,7 +3513,7 @@
         <v>465</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.5">
@@ -3405,7 +3524,7 @@
         <v>121</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.5">
@@ -3416,18 +3535,18 @@
         <v>993</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.5">
       <c r="A12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.5">
@@ -3435,55 +3554,55 @@
         <v>126</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.5">
       <c r="A14" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="B14" s="49" t="s">
+      <c r="C14" s="46" t="s">
         <v>203</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" s="50" t="s">
         <v>205</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="C15" s="46" t="s">
         <v>206</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="C16" s="46" t="s">
         <v>209</v>
-      </c>
-      <c r="C16" s="46" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" s="45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B17" s="50" t="str">
         <f>"D:\Procesos_UiPath\"&amp;Settings!B3&amp;"\"</f>
-        <v>D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\</v>
+        <v>D:\Procesos_UiPath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
@@ -3495,7 +3614,7 @@
       </c>
       <c r="B19" s="8" t="str">
         <f>"D:\Procesos_UiPath\"&amp;Settings!B3&amp;"\Archivos"</f>
-        <v>D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos</v>
+        <v>D:\Procesos_UiPath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>43</v>
@@ -3507,7 +3626,7 @@
       </c>
       <c r="B20" s="21" t="str">
         <f>"D:\Procesos_UiPath\"&amp;Settings!B3&amp;"\Archivos\Exceptions_Screenshots"</f>
-        <v>D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\Exceptions_Screenshots</v>
+        <v>D:\Procesos_UiPath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\Exceptions_Screenshots</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
@@ -3614,11 +3733,11 @@
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B30" s="47" t="str">
         <f>"D:\Procesos_UiPath\"&amp;Settings!B3&amp;"\Archivos\LOG"</f>
-        <v>D:\Procesos_UiPath\00_GENERICO_WINDOWS_NEGOCIOS_FINANCIEROS_XX_XX_XX\Archivos\LOG</v>
+        <v>D:\Procesos_UiPath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\LOG</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
@@ -5672,13 +5791,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D2" t="s">
         <v>45</v>
